--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD_PYRAD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.06</t>
+          <t>0.63 ± 0.06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.06</t>
+          <t>0.57 ± 0.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.56 ± 0.06</t>
+          <t>0.63 ± 0.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.11</t>
+          <t>0.53 ± 0.05</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.60 ± 0.12</t>
+          <t>0.62 ± 0.12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.54 ± 0.19</t>
+          <t>0.69 ± 0.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F4" t="n">
